--- a/EQDashboard_Setting.xlsx
+++ b/EQDashboard_Setting.xlsx
@@ -7,13 +7,13 @@
     <sheet name="Fabs" sheetId="2" r:id="rId2"/>
     <sheet name="Roles" sheetId="3" r:id="rId3"/>
     <sheet name="Accounts" sheetId="4" r:id="rId4"/>
-    <sheet name="App_Items" sheetId="5" r:id="rId5"/>
-    <sheet name="Requests" sheetId="6" r:id="rId6"/>
-    <sheet name="Map_Fab_Role" sheetId="7" r:id="rId7"/>
-    <sheet name="Map_Account_Role" sheetId="8" r:id="rId8"/>
-    <sheet name="Map_Account_ManageMenu" sheetId="9" r:id="rId9"/>
-    <sheet name="Map_Role_Menu" sheetId="10" r:id="rId10"/>
-    <sheet name="Map_Menu_Structure" sheetId="11" r:id="rId11"/>
+    <sheet name="Map_Fab_Role" sheetId="5" r:id="rId5"/>
+    <sheet name="Map_Account_Role" sheetId="6" r:id="rId6"/>
+    <sheet name="Map_Account_ManageMenu" sheetId="7" r:id="rId7"/>
+    <sheet name="Map_Role_Menu" sheetId="8" r:id="rId8"/>
+    <sheet name="Map_Menu_Structure" sheetId="9" r:id="rId9"/>
+    <sheet name="Map_Account_DefaultPage" sheetId="10" r:id="rId10"/>
+    <sheet name="PersonalSettings" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -478,14 +478,14 @@
       <c r="I2" t="str">
         <v>admin</v>
       </c>
-      <c r="J2" t="str">
-        <v>True</v>
-      </c>
-      <c r="K2" t="str">
-        <v>False</v>
-      </c>
-      <c r="L2" t="str">
-        <v>False</v>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -519,14 +519,14 @@
       <c r="I3" t="str">
         <v>admin</v>
       </c>
-      <c r="J3" t="str">
-        <v>True</v>
-      </c>
-      <c r="K3" t="str">
-        <v>False</v>
-      </c>
-      <c r="L3" t="str">
-        <v>False</v>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
       </c>
       <c r="M3">
         <v>10</v>
@@ -555,19 +555,19 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>fas fa-shield-alt</v>
       </c>
       <c r="I4" t="str">
         <v>admin</v>
       </c>
-      <c r="J4" t="str">
-        <v>True</v>
-      </c>
-      <c r="K4" t="str">
-        <v>False</v>
-      </c>
-      <c r="L4" t="str">
-        <v>True</v>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
       </c>
       <c r="M4">
         <v>20</v>
@@ -601,14 +601,14 @@
       <c r="I5" t="str">
         <v>admin</v>
       </c>
-      <c r="J5" t="str">
-        <v>True</v>
-      </c>
-      <c r="K5" t="str">
-        <v>True</v>
-      </c>
-      <c r="L5" t="str">
-        <v>False</v>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
       </c>
       <c r="M5">
         <v>30</v>
@@ -619,7 +619,7 @@
         <v>m_ze_2</v>
       </c>
       <c r="B6" t="str">
-        <v>WL子群組</v>
+        <v>WL</v>
       </c>
       <c r="C6" t="str">
         <v>WL子群組</v>
@@ -642,17 +642,17 @@
       <c r="I6" t="str">
         <v>admin</v>
       </c>
-      <c r="J6" t="str">
-        <v>True</v>
-      </c>
-      <c r="K6" t="str">
-        <v>False</v>
-      </c>
-      <c r="L6" t="str">
-        <v>True</v>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -675,22 +675,22 @@
         <v>page-ze-content</v>
       </c>
       <c r="G7" t="str">
-        <v>iframe</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>fas fa-desktop</v>
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>admin</v>
       </c>
-      <c r="J7" t="str">
-        <v>True</v>
-      </c>
-      <c r="K7" t="str">
-        <v>True</v>
-      </c>
-      <c r="L7" t="str">
-        <v>True</v>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
       </c>
       <c r="M7">
         <v>50</v>
@@ -698,13 +698,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>m_ze_3</v>
+        <v>m_ze_2_2</v>
       </c>
       <c r="B8" t="str">
-        <v>BSL</v>
+        <v>Non Scaling</v>
       </c>
       <c r="C8" t="str">
-        <v>BSL</v>
+        <v>Non Scaling</v>
       </c>
       <c r="D8" t="str">
         <v>link</v>
@@ -724,14 +724,14 @@
       <c r="I8" t="str">
         <v>admin</v>
       </c>
-      <c r="J8" t="str">
-        <v>True</v>
-      </c>
-      <c r="K8" t="str">
-        <v>True</v>
-      </c>
-      <c r="L8" t="str">
-        <v>False</v>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
       </c>
       <c r="M8">
         <v>60</v>
@@ -739,40 +739,40 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>m_fdc</v>
+        <v>m_ze_3</v>
       </c>
       <c r="B9" t="str">
-        <v>FDC 指標看板</v>
+        <v>BSL</v>
       </c>
       <c r="C9" t="str">
-        <v>FDC 指標看板</v>
+        <v>BSL</v>
       </c>
       <c r="D9" t="str">
         <v>link</v>
       </c>
       <c r="E9" t="str">
-        <v>https://tw.yahoo.com</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>page-ze-content</v>
       </c>
       <c r="G9" t="str">
-        <v>iframe</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>fas fa-table</v>
+        <v/>
       </c>
       <c r="I9" t="str">
         <v>admin</v>
       </c>
-      <c r="J9" t="str">
-        <v>True</v>
-      </c>
-      <c r="K9" t="str">
-        <v>False</v>
-      </c>
-      <c r="L9" t="str">
-        <v>False</v>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
       </c>
       <c r="M9">
         <v>70</v>
@@ -780,220 +780,243 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>m_app_test</v>
+        <v>m_fdc</v>
       </c>
       <c r="B10" t="str">
-        <v>12A_Module_TEST</v>
+        <v>FDC 指標看板</v>
       </c>
       <c r="C10" t="str">
-        <v>12A_Module</v>
+        <v>FDC 指標看板</v>
       </c>
       <c r="D10" t="str">
-        <v>folder</v>
+        <v>link</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>https://tw.yahoo.com</v>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>iframe</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>fas fa-table</v>
       </c>
       <c r="I10" t="str">
         <v>admin</v>
       </c>
-      <c r="J10" t="str">
-        <v>True</v>
-      </c>
-      <c r="K10" t="str">
-        <v>False</v>
-      </c>
-      <c r="L10" t="str">
-        <v>True</v>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>m_app_test</v>
+      </c>
+      <c r="B11" t="str">
+        <v>測試應用集合</v>
+      </c>
+      <c r="C11" t="str">
+        <v>12A_Module</v>
+      </c>
+      <c r="D11" t="str">
+        <v>app_grid</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>page-app-grid</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>fas fa-th-large</v>
+      </c>
+      <c r="I11" t="str">
+        <v>admin</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>m_12m</v>
+      </c>
+      <c r="B12" t="str">
+        <v>12M EAS</v>
+      </c>
+      <c r="C12" t="str">
+        <v>12M EAS</v>
+      </c>
+      <c r="D12" t="str">
+        <v>link</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>page-eas</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>fas fa-desktop</v>
+      </c>
+      <c r="I12" t="str">
+        <v>admin</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>RoleId</v>
+        <v>EmpId</v>
       </c>
       <c r="B1" t="str">
+        <v>FabId</v>
+      </c>
+      <c r="C1" t="str">
         <v>MenuId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>SortOrder</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>role_1</v>
+        <v>admin</v>
       </c>
       <c r="B2" t="str">
-        <v>m_eqas</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>12A</v>
+      </c>
+      <c r="C2" t="str">
+        <v>m_ze_1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>role_1</v>
+        <v>admin</v>
       </c>
       <c r="B3" t="str">
-        <v>m_eastest</v>
-      </c>
-      <c r="C3">
-        <v>20</v>
+        <v>12M</v>
+      </c>
+      <c r="C3" t="str">
+        <v>m_12m</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>role_1</v>
+        <v>admin</v>
       </c>
       <c r="B4" t="str">
-        <v>m_ze</v>
-      </c>
-      <c r="C4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>role_1</v>
-      </c>
-      <c r="B5" t="str">
+        <v>12i</v>
+      </c>
+      <c r="C4" t="str">
         <v>m_fdc</v>
-      </c>
-      <c r="C5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>role_1</v>
-      </c>
-      <c r="B6" t="str">
-        <v>m_app_test</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>role_2</v>
-      </c>
-      <c r="B7" t="str">
-        <v>m_12m</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>role_3</v>
-      </c>
-      <c r="B8" t="str">
-        <v>m_fdc</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>ParentMenuId</v>
+        <v>EmpId</v>
       </c>
       <c r="B1" t="str">
-        <v>ChildMenuId</v>
+        <v>MenuId</v>
       </c>
       <c r="C1" t="str">
+        <v>IsHidden</v>
+      </c>
+      <c r="D1" t="str">
+        <v>OpenTarget</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Icon</v>
+      </c>
+      <c r="F1" t="str">
         <v>SortOrder</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>m_ze</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>m_ze_1</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>m_ze</v>
-      </c>
-      <c r="B3" t="str">
-        <v>m_ze_2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>m_ze_2</v>
-      </c>
-      <c r="B4" t="str">
-        <v>m_ze_2_1</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>m_ze</v>
-      </c>
-      <c r="B5" t="str">
-        <v>m_ze_3</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1008,9 +1031,6 @@
       <c r="D1" t="str">
         <v>DefaultLang</v>
       </c>
-      <c r="E1" t="str">
-        <v>LangDisplayName</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1025,9 +1045,6 @@
       <c r="D2" t="str">
         <v>zh</v>
       </c>
-      <c r="E2" t="str">
-        <v>繁體中文</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1042,9 +1059,6 @@
       <c r="D3" t="str">
         <v>ja</v>
       </c>
-      <c r="E3" t="str">
-        <v>日本語</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1059,13 +1073,10 @@
       <c r="D4" t="str">
         <v>en</v>
       </c>
-      <c r="E4" t="str">
-        <v>English</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1115,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:E4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1133,9 +1144,6 @@
       <c r="E1" t="str">
         <v>CanEditOthers</v>
       </c>
-      <c r="F1" t="str">
-        <v>DefaultMenuId</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1150,11 +1158,8 @@
       <c r="D2" t="str">
         <v>admin</v>
       </c>
-      <c r="E2" t="str">
-        <v>False</v>
-      </c>
-      <c r="F2" t="str">
-        <v>m_fdc</v>
+      <c r="E2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1170,11 +1175,8 @@
       <c r="D3" t="str">
         <v>user</v>
       </c>
-      <c r="E3" t="str">
-        <v>False</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
+      <c r="E3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1182,49 +1184,26 @@
         <v>00058897</v>
       </c>
       <c r="B4" t="str">
-        <v>測試工程師</v>
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v>測試部</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v>user</v>
       </c>
-      <c r="E4" t="str">
-        <v>False</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
+      <c r="E4" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetData/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetData/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
   <sheetData>
@@ -1267,7 +1246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B9"/>
   <sheetData>
@@ -1350,9 +1329,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1370,25 +1349,185 @@
         <v>m_ze_2</v>
       </c>
     </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>RoleId</v>
+      </c>
+      <c r="B1" t="str">
+        <v>MenuId</v>
+      </c>
+      <c r="C1" t="str">
+        <v>SortOrder</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>role_1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>m_eqas</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>00058897</v>
+        <v>role_1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>m_eastest</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>role_1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>m_ze</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>role_1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>m_fdc</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>role_1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>m_app_test</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>role_2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>m_12m</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>role_3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>m_fdc</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ParentMenuId</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ChildMenuId</v>
+      </c>
+      <c r="C1" t="str">
+        <v>SortOrder</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>m_ze</v>
+      </c>
+      <c r="B2" t="str">
+        <v>m_ze_1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>m_ze</v>
       </c>
       <c r="B3" t="str">
         <v>m_ze_2</v>
       </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>00058897</v>
+        <v>m_ze_2</v>
       </c>
       <c r="B4" t="str">
-        <v>m_fdc</v>
+        <v>m_ze_2_1</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>m_ze_2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>m_ze_2_2</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>m_ze</v>
+      </c>
+      <c r="B6" t="str">
+        <v>m_ze_3</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>